--- a/manuscript_package/tables/table03_generalization_gaps.xlsx
+++ b/manuscript_package/tables/table03_generalization_gaps.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +27,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E8FB"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -411,228 +430,173 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>delta_r2_vs_random</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>delta_rmse_vs_random</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>delta_mae_vs_random</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Validation regime</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Delta R2 vs random</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta RMSE vs random</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta MAE vs random</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>group_aut</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>elastic_net</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.9176488337647434</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.4726719504095686</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0117172039889884</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by study</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>-0.473</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>group_aut</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>lightgbm</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>-10.62531745106325</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.143359616785251</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.7068749803194712</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by study</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>LGBM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>-10.625</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.707</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>group_aut</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>mlp_regressor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>-21745.45051847456</v>
-      </c>
-      <c r="D4" t="n">
-        <v>18.86234364669775</v>
-      </c>
-      <c r="E4" t="n">
-        <v>15.3044712716871</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by study</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>-21745.451</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>18.862</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>15.304</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>group_exp</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>elastic_net</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.003738731065382</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.1187644560834377</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.007386715169542</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by experiment</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>-0.119</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.007</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>group_exp</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>lightgbm</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.1456405436041919</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.2062773588475587</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.1232514749190654</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by experiment</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>LGBM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-0.146</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.123</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>group_exp</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>mlp_regressor</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.2091035979246035</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.4786351076019434</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.2447977863168246</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>leave_one_study_out</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>elastic_net</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>-1879.096007058941</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.8547168035389343</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.2285067486812272</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>leave_one_study_out</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lightgbm</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>-158.0145135073176</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.6458249458622594</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.8727228306452337</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>leave_one_study_out</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mlp_regressor</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>-206692.4605566344</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3.582173044695158</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3.488107098892812</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by experiment</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-0.209</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.245</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>